--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_la_araucania.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:47</t>
+    <t xml:space="preserve">2026-09-24 00:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -540,16 +540,16 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.14</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>32</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.24</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>0.1</v>
@@ -572,7 +572,7 @@
         <v>-0.31</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>-0.05</v>
@@ -586,16 +586,16 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>32</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>-0.05</v>
@@ -618,10 +618,10 @@
         <v>0.22</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="6">
@@ -632,7 +632,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>32</v>
@@ -641,7 +641,7 @@
         <v>0.32</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>-0.31</v>
@@ -655,19 +655,19 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>32</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="8">
@@ -684,13 +684,13 @@
         <v>32</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="9">
@@ -707,13 +707,13 @@
         <v>32</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="10">
@@ -730,13 +730,13 @@
         <v>32</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.06</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="11">
@@ -753,13 +753,13 @@
         <v>32</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="12">
@@ -770,19 +770,19 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>32</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="13">
@@ -799,13 +799,13 @@
         <v>32</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="14">
@@ -816,19 +816,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>32</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="15">
@@ -839,16 +839,16 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>32</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>0.04</v>
@@ -871,7 +871,7 @@
         <v>0.15</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>0.01</v>
@@ -885,19 +885,19 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>32</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="18">
@@ -917,7 +917,7 @@
         <v>-0.41</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>-0.04</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_la_araucania.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:38</t>
+    <t xml:space="preserve">2026-10-01 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_la_araucania.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2018_la_araucania.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:11</t>
+    <t xml:space="preserve">2026-10-05 19:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
